--- a/templates/angelica_brief/plantilla_reel_angelica.xlsx
+++ b/templates/angelica_brief/plantilla_reel_angelica.xlsx
@@ -441,15 +441,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -480,10 +478,10 @@
       </c>
       <c r="B3" t="inlineStr"/>
     </row>
-    <row r="4" ht="36" customHeight="1">
+    <row r="4" ht="48" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Tiempos = TU video original (no Instagram). Pega la foto en Foto. Lado: derecha, izquierda o arriba. Sin foto = título en el cielo (escribe Texto). La tarjeta de WhatsApp del final se pone sola.</t>
+          <t>Escribe con tus palabras. Reloj = TU video, no Instagram. Pega la foto en Foto. En «Qué quieres» di qué se ve y dónde (derecha / izquierda / arriba). Si dos fotos se ven juntas, son dos filas. Cursor arma el reel.</t>
         </is>
       </c>
     </row>
@@ -505,80 +503,77 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Texto</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Lado</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Nota</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="64" customHeight="1">
+          <t>Qué quieres</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="88" customHeight="1">
       <c r="A7" s="4" t="n"/>
       <c r="B7" s="4" t="n"/>
-    </row>
-    <row r="8" ht="64" customHeight="1">
+      <c r="D7" s="4" t="n"/>
+    </row>
+    <row r="8" ht="88" customHeight="1">
       <c r="A8" s="4" t="n"/>
       <c r="B8" s="4" t="n"/>
-    </row>
-    <row r="9" ht="64" customHeight="1">
+      <c r="D8" s="4" t="n"/>
+    </row>
+    <row r="9" ht="88" customHeight="1">
       <c r="A9" s="4" t="n"/>
       <c r="B9" s="4" t="n"/>
-    </row>
-    <row r="10" ht="64" customHeight="1">
+      <c r="D9" s="4" t="n"/>
+    </row>
+    <row r="10" ht="88" customHeight="1">
       <c r="A10" s="4" t="n"/>
       <c r="B10" s="4" t="n"/>
-    </row>
-    <row r="11" ht="64" customHeight="1">
+      <c r="D10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="88" customHeight="1">
       <c r="A11" s="4" t="n"/>
       <c r="B11" s="4" t="n"/>
-    </row>
-    <row r="12" ht="64" customHeight="1">
+      <c r="D11" s="4" t="n"/>
+    </row>
+    <row r="12" ht="88" customHeight="1">
       <c r="A12" s="4" t="n"/>
       <c r="B12" s="4" t="n"/>
-    </row>
-    <row r="13" ht="64" customHeight="1">
+      <c r="D12" s="4" t="n"/>
+    </row>
+    <row r="13" ht="88" customHeight="1">
       <c r="A13" s="4" t="n"/>
       <c r="B13" s="4" t="n"/>
-    </row>
-    <row r="14" ht="64" customHeight="1">
+      <c r="D13" s="4" t="n"/>
+    </row>
+    <row r="14" ht="88" customHeight="1">
       <c r="A14" s="4" t="n"/>
       <c r="B14" s="4" t="n"/>
-    </row>
-    <row r="15" ht="64" customHeight="1">
+      <c r="D14" s="4" t="n"/>
+    </row>
+    <row r="15" ht="88" customHeight="1">
       <c r="A15" s="4" t="n"/>
       <c r="B15" s="4" t="n"/>
-    </row>
-    <row r="16" ht="64" customHeight="1">
+      <c r="D15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="88" customHeight="1">
       <c r="A16" s="4" t="n"/>
       <c r="B16" s="4" t="n"/>
-    </row>
-    <row r="17" ht="64" customHeight="1">
+      <c r="D16" s="4" t="n"/>
+    </row>
+    <row r="17" ht="88" customHeight="1">
       <c r="A17" s="4" t="n"/>
       <c r="B17" s="4" t="n"/>
-    </row>
-    <row r="18" ht="64" customHeight="1">
+      <c r="D17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="88" customHeight="1">
       <c r="A18" s="4" t="n"/>
       <c r="B18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="E7:E18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="derecha / izquierda de la cabeza, o arriba (título)" type="list">
-      <formula1>"derecha,izquierda,arriba"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/templates/angelica_brief/plantilla_reel_angelica.xlsx
+++ b/templates/angelica_brief/plantilla_reel_angelica.xlsx
@@ -1,54 +1,171 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thorstenbrueckner/Documents/GitHub/thor/video-editor/templates/angelica_brief/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ACECCCF-CE27-704D-8DBE-21A901019920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Brief" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Brief" sheetId="1" r:id="rId1"/>
+    <sheet name="Instrucciones" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+  <si>
+    <t>Título</t>
+  </si>
+  <si>
+    <t>Cortar al inicio (segundos)</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Terminas de hablar (reloj de TU video)</t>
+  </si>
+  <si>
+    <t>Tiempos: 1:29,5 (minutos:segundos, décimos con coma). No hace falta al frame. Reloj = TU video. Pega la foto del tamaño que sea. En «Qué quieres»: qué se ve, dónde (derecha / izquierda / arriba) y tamaño (grande / mediano / chico). Dos fotos juntas = dos filas. Ver pestaña Instrucciones.</t>
+  </si>
+  <si>
+    <t>Desde</t>
+  </si>
+  <si>
+    <t>Hasta</t>
+  </si>
+  <si>
+    <t>Foto</t>
+  </si>
+  <si>
+    <t>Qué quieres</t>
+  </si>
+  <si>
+    <t>Cómo llenar el Brief</t>
+  </si>
+  <si>
+    <t>Manda el video + esta Excel. Escribe como hables. Cursor arma el reel.
+Los subtítulos salen solos: no los marques aquí.</t>
+  </si>
+  <si>
+    <t>Arriba (pestaña Brief)</t>
+  </si>
+  <si>
+    <t>• Título del reel.
+• Cortar al inicio: segundos de silencio o toma fallida (ej. 4).
+• Terminas de hablar: reloj de TU video (ej. 1:29,5).</t>
+  </si>
+  <si>
+    <t>Una fila por cosa que se ve</t>
+  </si>
+  <si>
+    <t>Desde / Hasta / pega la Foto / Qué quieres.</t>
+  </si>
+  <si>
+    <t>Si dos fotos se ven juntas (frutero + susto), son DOS filas que se solapan.
+Sin foto = títulos (tu nombre, Medicina Familiar, ENFOQUE INTEGRAL).
+La tarjeta de WhatsApp del final no va aquí: sale sola.</t>
+  </si>
+  <si>
+    <t>Tiempos (reloj de TU grabación)</t>
+  </si>
+  <si>
+    <t>No uses el reloj del Instagram ya publicado.
+No hace falta al frame (ni 0:05.50 ni fotogramas). Un décimo de segundo basta.</t>
+  </si>
+  <si>
+    <t>Escribe minutos:segundos, y si hace falta un décimo con COMA:</t>
+  </si>
+  <si>
+    <t>• 0:28 = segundo 28 de tu video
+• 1:29,5 = 1 minuto 29 segundos y medio
+• 10:25,5 = 10 minutos 25 segundos y medio</t>
+  </si>
+  <si>
+    <t>La coma evita que Excel lo convierta en hora del día. No pongas tres números (1:29:15).</t>
+  </si>
+  <si>
+    <t>Como hables: qué se ve, derecha / izquierda / arriba, si se suma a otra foto,
+y el tamaño (grande, mediano o chico). Pega la foto como la encuentres,
+del tamaño que sea. No recortes a pixels.</t>
+  </si>
+  <si>
+    <t>No pongas fotos encima de la cabeza / gorro.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00068A93"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF068A93"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="00666666"/>
+      <i/>
       <sz val="11"/>
+      <color rgb="FF666666"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF068A93"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00068A93"/>
+        <fgColor rgb="FF068A93"/>
       </patternFill>
     </fill>
   </fills>
@@ -64,91 +181,46 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -436,136 +508,123 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="72" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="33" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="34.1640625" customWidth="1"/>
+    <col min="4" max="4" width="72" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Título</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr"/>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Cortar al inicio (segundos)</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Terminas de hablar (reloj de TU video)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-    </row>
-    <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Escribe con tus palabras. Reloj = TU video, no Instagram. Pega la foto en Foto. En «Qué quieres» di qué se ve y dónde (derecha / izquierda / arriba). Si dos fotos se ven juntas, son dos filas. Cursor arma el reel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Desde</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Hasta</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Foto</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Qué quieres</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="88" customHeight="1">
-      <c r="A7" s="4" t="n"/>
-      <c r="B7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-    </row>
-    <row r="8" ht="88" customHeight="1">
-      <c r="A8" s="4" t="n"/>
-      <c r="B8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
-    </row>
-    <row r="9" ht="88" customHeight="1">
-      <c r="A9" s="4" t="n"/>
-      <c r="B9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-    </row>
-    <row r="10" ht="88" customHeight="1">
-      <c r="A10" s="4" t="n"/>
-      <c r="B10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-    </row>
-    <row r="11" ht="88" customHeight="1">
-      <c r="A11" s="4" t="n"/>
-      <c r="B11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-    </row>
-    <row r="12" ht="88" customHeight="1">
-      <c r="A12" s="4" t="n"/>
-      <c r="B12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-    </row>
-    <row r="13" ht="88" customHeight="1">
-      <c r="A13" s="4" t="n"/>
-      <c r="B13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-    </row>
-    <row r="14" ht="88" customHeight="1">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-    </row>
-    <row r="15" ht="88" customHeight="1">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-    </row>
-    <row r="16" ht="88" customHeight="1">
-      <c r="A16" s="4" t="n"/>
-      <c r="B16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-    </row>
-    <row r="17" ht="88" customHeight="1">
-      <c r="A17" s="4" t="n"/>
-      <c r="B17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-    </row>
-    <row r="18" ht="88" customHeight="1">
-      <c r="A18" s="4" t="n"/>
-      <c r="B18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
+    <row r="1" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+    </row>
+    <row r="2" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+    </row>
+    <row r="3" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="7"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+    </row>
+    <row r="4" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+    </row>
+    <row r="6" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="88" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" ht="88" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:4" ht="88" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="1:4" ht="88" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="D10" s="4"/>
+    </row>
+    <row r="11" spans="1:4" ht="88" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="D11" s="4"/>
+    </row>
+    <row r="12" spans="1:4" ht="88" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="D12" s="4"/>
+    </row>
+    <row r="13" spans="1:4" ht="88" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="D13" s="4"/>
+    </row>
+    <row r="14" spans="1:4" ht="88" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="D14" s="4"/>
+    </row>
+    <row r="15" spans="1:4" ht="88" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="D15" s="4"/>
+    </row>
+    <row r="16" spans="1:4" ht="88" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="D16" s="4"/>
+    </row>
+    <row r="17" spans="1:4" ht="88" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="D17" s="4"/>
+    </row>
+    <row r="18" spans="1:4" ht="88" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="D18" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -576,4 +635,125 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="88" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="5"/>
+    </row>
+    <row r="3" spans="1:2" ht="44" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="5"/>
+    </row>
+    <row r="5" spans="1:2" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="5"/>
+    </row>
+    <row r="6" spans="1:2" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="5"/>
+    </row>
+    <row r="8" spans="1:2" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="5"/>
+    </row>
+    <row r="9" spans="1:2" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="5"/>
+    </row>
+    <row r="11" spans="1:2" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="5"/>
+    </row>
+    <row r="13" spans="1:2" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="5"/>
+    </row>
+    <row r="14" spans="1:2" ht="44" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="5"/>
+    </row>
+    <row r="16" spans="1:2" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="5"/>
+    </row>
+    <row r="18" spans="1:2" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="5"/>
+    </row>
+    <row r="20" spans="1:2" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="5"/>
+    </row>
+    <row r="22" spans="1:2" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="5"/>
+    </row>
+    <row r="23" spans="1:2" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="5"/>
+    </row>
+    <row r="25" spans="1:2" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A22:B22"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>